--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -60,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -68,6 +68,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,12 +528,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -575,12 +576,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -618,12 +619,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -661,12 +662,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -704,12 +705,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -747,12 +748,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -795,12 +796,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -838,12 +839,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -881,12 +882,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
     </row>
@@ -924,12 +925,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
     </row>
@@ -967,12 +968,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1011,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1054,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1101,12 +1102,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:30</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1150,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:20</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1193,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1236,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1279,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1327,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1370,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1413,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:50</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1456,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1504,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1552,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1595,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1638,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1685,12 +1686,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1734,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:20</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1777,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1820,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1863,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:40</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1911,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:45</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1954,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:50</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1997,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2040,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2088,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
     </row>
@@ -2130,12 +2131,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2174,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2217,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2269,12 +2270,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2313,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2356,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2399,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -2441,12 +2442,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2490,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2533,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2576,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -2618,12 +2619,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2667,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2710,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2753,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2796,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -2848,12 +2849,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2892,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2935,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -2977,12 +2978,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3026,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3069,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3112,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3155,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -3197,12 +3198,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3241,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
     </row>
@@ -3283,12 +3284,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3327,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
     </row>
@@ -3369,12 +3370,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3422,12 +3423,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:30</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3466,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:20</t>
         </is>
       </c>
     </row>
@@ -3508,12 +3509,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3552,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3600,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -3642,12 +3643,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3686,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3729,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:50</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3777,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -3819,12 +3820,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -3862,12 +3863,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -3905,12 +3906,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -3953,12 +3954,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4001,12 +4002,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
     </row>
@@ -4044,12 +4045,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:20</t>
         </is>
       </c>
     </row>
@@ -4087,12 +4088,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4131,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
     </row>
@@ -4178,12 +4179,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:40</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4222,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:45</t>
         </is>
       </c>
     </row>
@@ -4264,12 +4265,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:50</t>
         </is>
       </c>
     </row>
@@ -4307,12 +4308,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:55</t>
         </is>
       </c>
     </row>
@@ -4355,12 +4356,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4399,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4442,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4485,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
     </row>
@@ -4532,12 +4533,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4580,12 +4581,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4624,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4667,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4715,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4758,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -4800,12 +4801,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4844,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -4886,12 +4887,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4935,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -4977,12 +4978,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5021,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5064,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -5111,12 +5112,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -5159,12 +5160,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -5202,12 +5203,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -5245,12 +5246,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -5293,12 +5294,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5337,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5380,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -5422,12 +5423,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -5470,12 +5471,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -5513,12 +5514,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
     </row>
@@ -5556,12 +5557,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
     </row>
@@ -5599,12 +5600,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5643,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5686,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -5733,12 +5734,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:30</t>
         </is>
       </c>
     </row>
@@ -5776,12 +5777,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:25</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5820,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:15</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5868,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
     </row>
@@ -5910,12 +5911,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -5953,12 +5954,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -5996,12 +5997,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6045,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6088,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:50</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6131,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6174,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -6221,12 +6222,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -6264,12 +6265,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -6307,12 +6308,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -6355,12 +6356,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:20</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6404,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6447,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
     </row>
@@ -6489,12 +6490,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:40</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6533,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:45</t>
         </is>
       </c>
     </row>
@@ -6575,12 +6576,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:50</t>
         </is>
       </c>
     </row>
@@ -6623,12 +6624,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:55</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6667,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -6709,12 +6710,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
     </row>
@@ -6752,12 +6753,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6801,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
     </row>
@@ -6843,12 +6844,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6887,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -6934,12 +6935,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6983,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -7025,12 +7026,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -7068,12 +7069,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7112,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -7159,12 +7160,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -7202,12 +7203,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -7245,12 +7246,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -7288,12 +7289,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -7336,12 +7337,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -7384,12 +7385,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -7427,12 +7428,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -7470,12 +7471,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -7518,12 +7519,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7567,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -7609,12 +7610,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -7652,12 +7653,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -7695,12 +7696,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -7743,12 +7744,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7787,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -7829,12 +7830,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -7872,12 +7873,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
     </row>
@@ -7915,12 +7916,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -7958,12 +7959,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
     </row>
@@ -8001,12 +8002,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
     </row>
@@ -8044,12 +8045,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -8097,12 +8098,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:25</t>
         </is>
       </c>
     </row>
@@ -8140,12 +8141,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:15</t>
         </is>
       </c>
     </row>
@@ -8183,12 +8184,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8227,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8270,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8318,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -8360,12 +8361,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -8403,12 +8404,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:50</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8447,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -8494,12 +8495,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -8537,12 +8538,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8581,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -8623,12 +8624,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -8676,12 +8677,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:20</t>
         </is>
       </c>
     </row>
@@ -8719,12 +8720,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
     </row>
@@ -8762,12 +8763,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8806,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
     </row>
@@ -8853,12 +8854,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:45</t>
         </is>
       </c>
     </row>
@@ -8896,12 +8897,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:50</t>
         </is>
       </c>
     </row>
@@ -8939,12 +8940,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:55</t>
         </is>
       </c>
     </row>
@@ -8982,12 +8983,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -9030,12 +9031,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
     </row>
@@ -9073,12 +9074,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
     </row>
@@ -9116,12 +9117,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
     </row>
@@ -9159,12 +9160,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -9202,12 +9203,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -9255,12 +9256,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -9298,12 +9299,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9342,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -9384,12 +9385,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -9432,12 +9433,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -9470,12 +9471,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -9513,12 +9514,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -9556,12 +9557,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9605,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -9647,12 +9648,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -9690,12 +9691,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -9733,12 +9734,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -9781,12 +9782,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -9829,12 +9830,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -9872,12 +9873,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -9915,12 +9916,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -9963,12 +9964,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -10011,12 +10012,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10055,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -10097,12 +10098,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -10140,12 +10141,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -10183,12 +10184,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
     </row>
@@ -10226,12 +10227,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -10269,12 +10270,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
     </row>
@@ -10312,12 +10313,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10361,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -10408,12 +10409,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:25</t>
         </is>
       </c>
     </row>
@@ -10451,12 +10452,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:20</t>
         </is>
       </c>
     </row>
@@ -10494,12 +10495,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
     </row>
@@ -10542,12 +10543,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -10585,12 +10586,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10629,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -10671,12 +10672,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -10719,12 +10720,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:50</t>
         </is>
       </c>
     </row>
@@ -10762,12 +10763,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -10805,12 +10806,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -10848,12 +10849,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -10896,12 +10897,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -10939,12 +10940,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -10987,12 +10988,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
     </row>
@@ -11030,12 +11031,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
     </row>
@@ -11073,12 +11074,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
     </row>
@@ -11121,12 +11122,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
     </row>
@@ -11164,12 +11165,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:40</t>
         </is>
       </c>
     </row>
@@ -11207,12 +11208,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:50</t>
         </is>
       </c>
     </row>
@@ -11250,12 +11251,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:55</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11299,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -11341,12 +11342,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
     </row>
@@ -11384,12 +11385,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
     </row>
@@ -11427,12 +11428,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:15</t>
         </is>
       </c>
     </row>
@@ -11475,12 +11476,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -11518,12 +11519,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -11566,12 +11567,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -11609,12 +11610,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -11657,12 +11658,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -11700,12 +11701,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -11743,12 +11744,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -11786,12 +11787,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -11829,12 +11830,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -11877,12 +11878,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -11920,12 +11921,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -11963,12 +11964,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -12006,12 +12007,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -12054,12 +12055,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -12097,12 +12098,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -12145,12 +12146,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -12188,12 +12189,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -12236,12 +12237,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -12279,12 +12280,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -12322,12 +12323,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -12365,12 +12366,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -12413,12 +12414,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -12456,12 +12457,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -12499,12 +12500,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
     </row>
@@ -12542,12 +12543,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
     </row>
@@ -12585,12 +12586,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
     </row>
@@ -12628,12 +12629,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
     </row>
@@ -12759,37 +12760,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>46122</v>
+      <c r="A2" s="5" t="n">
+        <v>46304</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>שמיני</t>
+          <t>בראשית</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>שמיני</t>
+          <t>בראשית</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12819,37 +12820,37 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">

--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -60,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -68,7 +68,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,12 +527,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -576,12 +575,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -619,7 +618,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -667,7 +666,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -705,12 +704,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -796,12 +795,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -839,12 +838,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -882,7 +881,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -968,12 +967,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1010,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1053,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1102,7 +1101,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1150,12 +1149,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:25</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1235,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:10</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1278,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1326,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1369,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1413,12 +1412,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1455,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1509,7 +1508,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1551,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1595,7 +1594,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1638,7 +1637,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1686,12 +1685,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:20</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1733,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1819,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1863,12 +1862,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1910,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:50</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1958,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:55</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1996,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2040,7 +2039,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2088,7 +2087,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2131,12 +2130,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2173,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2221,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2275,7 +2274,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2317,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2360,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2403,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2446,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2494,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -2533,12 +2532,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2575,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2618,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2672,7 +2671,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -2710,12 +2709,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -2753,12 +2752,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2795,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -2854,7 +2853,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2891,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2935,7 +2934,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2978,7 +2977,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3026,12 +3025,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -3069,12 +3068,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -3112,12 +3111,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3197,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -3241,12 +3240,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3283,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3326,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3369,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3423,12 +3422,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:35</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3465,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:25</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3508,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3557,7 +3556,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:10</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3604,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -3643,12 +3642,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3685,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3729,12 +3728,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3776,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3820,12 +3819,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3862,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3906,7 +3905,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3954,7 +3953,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4002,7 +4001,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4045,12 +4044,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
     </row>
@@ -4088,12 +4087,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:30</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4130,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4179,7 +4178,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4222,12 +4221,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:50</t>
         </is>
       </c>
     </row>
@@ -4265,12 +4264,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:55</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4312,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4360,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:05</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4403,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:10</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4446,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4489,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4532,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4581,12 +4580,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4623,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4666,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4714,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -4758,12 +4757,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -4801,12 +4800,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4843,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4886,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -4935,7 +4934,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -4983,7 +4982,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5020,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -5064,12 +5063,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -5112,12 +5111,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -5165,7 +5164,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5202,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5246,7 +5245,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5294,7 +5293,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5337,7 +5336,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5380,12 +5379,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -5471,12 +5470,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -5514,12 +5513,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5556,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5600,7 +5599,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -5686,12 +5685,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -5734,12 +5733,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:35</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5776,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -5820,12 +5819,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:20</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5867,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -5911,12 +5910,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5953,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -5997,12 +5996,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6044,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6088,12 +6087,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6130,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6174,12 +6173,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6226,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6269,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:10</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6355,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6404,12 +6403,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:30</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6446,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:35</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6489,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6533,7 +6532,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6576,12 +6575,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:55</t>
         </is>
       </c>
     </row>
@@ -6624,12 +6623,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6666,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:05</t>
         </is>
       </c>
     </row>
@@ -6710,12 +6709,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:10</t>
         </is>
       </c>
     </row>
@@ -6753,12 +6752,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6800,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6843,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6886,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -6935,12 +6934,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -6983,12 +6982,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -7026,12 +7025,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:45</t>
         </is>
       </c>
     </row>
@@ -7069,12 +7068,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7111,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7159,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -7203,7 +7202,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -7246,12 +7245,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7288,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -7337,12 +7336,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -7385,12 +7384,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7427,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -7471,12 +7470,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -7519,7 +7518,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -7567,12 +7566,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -7610,12 +7609,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -7653,12 +7652,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -7744,12 +7743,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7786,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7829,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -7916,12 +7915,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
     </row>
@@ -7959,12 +7958,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8001,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8044,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -8098,7 +8097,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -8141,12 +8140,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:20</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8183,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -8227,7 +8226,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -8270,7 +8269,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -8323,7 +8322,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8360,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -8404,12 +8403,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8446,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -8495,12 +8494,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8537,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8580,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:10</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8623,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -8720,7 +8719,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -8763,12 +8762,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:35</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8810,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8853,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -8897,7 +8896,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -8940,12 +8939,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
@@ -8983,12 +8982,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:05</t>
         </is>
       </c>
     </row>
@@ -9031,12 +9030,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:10</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9073,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
     </row>
@@ -9117,12 +9116,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:20</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9159,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9202,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -9256,7 +9255,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -9299,7 +9298,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -9342,7 +9341,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -9385,7 +9384,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -9433,7 +9432,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -9471,7 +9470,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -9514,7 +9513,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -9557,12 +9556,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9604,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -9648,12 +9647,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -9691,12 +9690,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9733,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -9782,12 +9781,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -9830,7 +9829,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -9873,12 +9872,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -9916,12 +9915,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -9964,12 +9963,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10011,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -10055,12 +10054,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:40</t>
         </is>
       </c>
     </row>
@@ -10141,12 +10140,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -10184,12 +10183,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
     </row>
@@ -10227,12 +10226,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
     </row>
@@ -10270,12 +10269,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10312,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -10409,12 +10408,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:30</t>
         </is>
       </c>
     </row>
@@ -10495,12 +10494,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10542,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -10586,7 +10585,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -10634,7 +10633,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10671,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -10720,12 +10719,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10762,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -10811,7 +10810,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
@@ -10849,12 +10848,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
     </row>
@@ -10897,12 +10896,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:10</t>
         </is>
       </c>
     </row>
@@ -10940,12 +10939,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -10988,12 +10987,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:20</t>
         </is>
       </c>
     </row>
@@ -11031,7 +11030,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -11074,12 +11073,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:35</t>
         </is>
       </c>
     </row>
@@ -11122,12 +11121,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:40</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11169,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11207,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -11251,7 +11250,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -11299,7 +11298,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -11342,7 +11341,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -11385,7 +11384,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -11428,7 +11427,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -11476,7 +11475,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -11519,7 +11518,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -11567,7 +11566,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -11610,7 +11609,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -11658,7 +11657,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -11701,7 +11700,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -11744,7 +11743,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -11787,7 +11786,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -11830,12 +11829,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11882,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11920,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -11964,12 +11963,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -12007,12 +12006,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -12055,12 +12054,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -12098,12 +12097,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -12146,12 +12145,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
@@ -12194,7 +12193,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:05</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12241,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -12280,12 +12279,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:55</t>
         </is>
       </c>
     </row>
@@ -12323,12 +12322,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:50</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12365,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -12414,12 +12413,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
     </row>
@@ -12457,12 +12456,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
     </row>
@@ -12500,12 +12499,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12542,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -12629,12 +12628,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:50</t>
         </is>
       </c>
     </row>
@@ -12760,37 +12759,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>46304</v>
+      <c r="A2" s="4" t="n">
+        <v>46318</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>בראשית</t>
+          <t>לך־לך</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>בראשית</t>
+          <t>לך־לך</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12805,7 +12804,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -12820,42 +12819,42 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>16:35</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>כן</t>
+          <t>לא</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>

--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -60,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -68,6 +68,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12759,7 +12760,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="5" t="n">
         <v>46318</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -12804,7 +12805,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">

--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -12805,7 +12805,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">

--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -60,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -68,7 +68,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12760,37 +12759,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>46318</v>
+      <c r="A2" s="4" t="n">
+        <v>46325</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>לך־לך</t>
+          <t>וירא</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>לך־לך</t>
+          <t>וירא</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12800,7 +12799,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -12815,42 +12814,42 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">

--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -12760,36 +12760,36 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46325</v>
+        <v>46500</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>23/04/2027</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>וירא</t>
+          <t>פסח</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>וירא</t>
+          <t>פסח</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12819,37 +12819,37 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">

--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -12760,36 +12760,36 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46500</v>
+        <v>46325</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23/04/2027</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>פסח</t>
+          <t>וירא</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>פסח</t>
+          <t>וירא</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12804,52 +12804,52 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>14:00 / 17:00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>18:55</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">

--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -12760,36 +12760,36 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>וירא</t>
+          <t>חיי שרה</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>וירא</t>
+          <t>חיי שרה</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12819,42 +12819,42 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>לא</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
